--- a/datas/2025/2025.xlsx
+++ b/datas/2025/2025.xlsx
@@ -19130,63 +19130,58 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>VIR CPTE A CPTE EMIS VR.PERMANENT ELECTRICITE FH</t>
+          <t>MAYLOC / SPEEDY STRASBOURG</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>419.33</v>
       </c>
     </row>
     <row r="3">
       <c r="G3" s="2" t="n"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>VIR CPTE A CPTE EMIS VR.PERMANENT FREE FH INTRNET ET MOBILE</t>
+          <t>DEJBOX MARCQ EN BARO</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>46</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="4">
       <c r="G4" s="2" t="n"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE HABITATION FH</t>
+          <t>OVERGROUND STRASBOURG</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -19218,21 +19213,21 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE FONCIERE FH</t>
+          <t>GOOGLE PLAY APP</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>70</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
@@ -19264,16 +19259,21 @@
       <c r="G6" s="2" t="n"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>29/07/2025</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M HOONAKKER FRANK /MOTIF HOT</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>100</v>
+          <t>AUCHAN SUPERMAR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -19305,7 +19305,7 @@
       <c r="G7" s="2" t="n"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -19315,11 +19315,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>HOTEL KREUZ-PO</t>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>102</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="8">
@@ -19351,16 +19351,21 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>29/07/2025</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CULBERSON CHRIST /MOTIF PEA</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>75</v>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>32.37</v>
       </c>
     </row>
     <row r="9">
@@ -19392,21 +19397,16 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>HOTEL KREUZ POS</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>35.8</v>
+          <t>NOVALIX SAS /MOTIF VIREMENT SAS NOVALIX</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>3261.44</v>
       </c>
     </row>
     <row r="10">
@@ -19438,21 +19438,21 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AMAZON PRIME FR PAYLI2469664/</t>
+          <t>PAYPAL *KOMOOT LUXEMBOURG</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>69.90000000000001</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="11">
@@ -19484,21 +19484,16 @@
       <c r="G11" s="2" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>QUITOQUE PARIS</t>
+          <t>VIR CPTE A CPTE EMIS /MOTIF RESTE FIN DE MOIS /BEN M HOONAKKER FRANK /REFDO /REFBEN</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>92.89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -19530,21 +19525,21 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Vt vers : 30004031840003113585558</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>150</v>
+          <t>MHP PRESTATIONS SANTE PLEIADE /MOTIF HOONAKKER FRANK(N252050696A)</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4.34</v>
       </c>
     </row>
     <row r="13">
@@ -19576,21 +19571,21 @@
       <c r="G13" s="2" t="n"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>MACIF CENTRE EUROPE PRODUCTION-MACIF</t>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>117.68</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14">
@@ -19622,7 +19617,7 @@
       <c r="G14" s="2" t="n"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -19632,11 +19627,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ARIANE PIZZA STRASBOURG</t>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="15">
@@ -19668,21 +19663,21 @@
       <c r="G15" s="2" t="n"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SNCF-VOYAGEURS PARIS 10</t>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>20.9</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="16">
@@ -19714,21 +19709,21 @@
       <c r="G16" s="2" t="n"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>INTERSPORT STUTZHEIM OFF</t>
+          <t>LEROY MERLIN OSTWALD</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="17">
@@ -19760,21 +19755,21 @@
       <c r="G17" s="2" t="n"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ECHEANCE PRET 03184 60645874 (CAPITAL DU 105,38 EUR)</t>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.88</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="18">
@@ -19806,21 +19801,16 @@
       <c r="G18" s="2" t="n"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ECHEANCE PRET 03184 60236534 (CAPITAL DU 502,76 EUR)</t>
+          <t>HELLOCSE LYON 7EME</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>172.03</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -19852,7 +19842,7 @@
       <c r="G19" s="2" t="n"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>03/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -19862,11 +19852,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AUCHAN SUPERMAR STRASBOURG</t>
+          <t>LIDL LINGO 3782 LINGOLSHEIM</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.19</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="20">
@@ -19898,21 +19888,21 @@
       <c r="G20" s="2" t="n"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>03/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+          <t>QUITOQUE PARIS</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.78</v>
+        <v>92.89</v>
       </c>
     </row>
     <row r="21">
@@ -19944,21 +19934,21 @@
       <c r="G21" s="2" t="n"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>03/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+          <t>LOU-ANNE /REFDO LIVRE</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -19990,21 +19980,21 @@
       <c r="G22" s="2" t="n"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL PAYLI2090401/</t>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.75</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="23">
@@ -20036,21 +20026,21 @@
       <c r="G23" s="2" t="n"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>24/07/2025</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>FREE MOBILE</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>5.99</v>
+          <t>CPAM DU BAS-RHIN - STRAS /MOTIF 252040002846</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>29.14</v>
       </c>
     </row>
     <row r="24">
@@ -20082,21 +20072,16 @@
       <c r="G24" s="2" t="n"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>VIREMENT FAVEUR TIERS VR.PERMANENT PRET IMMOBILIER</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>550</v>
+          <t>M HOONAKKER FRANK /MOTIF MAISON</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="25">
@@ -20128,283 +20113,1290 @@
       <c r="G25" s="2" t="n"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL PAYLI2090401/</t>
+          <t>VIR CPTE A CPTE EMIS /MOTIF MAISON /BEN M HOONAKKER FRANK /REFDO /REFBEN</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>7.79</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="26">
       <c r="G26" s="2" t="n"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MC DONALD S STRASBOURG</t>
+          <t>VIR CPTE A CPTE EMIS /MOTIF MAISON /BEN M HOONAKKER FRANK /REFDO /REFBEN</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>16.5</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="27">
       <c r="G27" s="2" t="n"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>VIREMENT FAVEUR TIERS VR.PERMANENT ASSURANCE PRET FH</t>
+          <t>VIR CPTE A CPTE EMIS /MOTIF MAISON /BEN M HOONAKKER FRANK /REFDO /REFBEN</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>67</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="28">
       <c r="G28" s="2" t="n"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>VIR CPTE A CPTE EMIS VR.PERMANENT GAZ FH</t>
+          <t>SELARL DR NINIS STRASBOURG</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>95</v>
+        <v>43.38</v>
       </c>
     </row>
     <row r="29">
       <c r="G29" s="2" t="n"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>VIREMENT FAVEUR TIERS VR.PERMANENT MOIS LA</t>
+          <t>ESPACE MARJANE STRASBOURG</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>255</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="30">
       <c r="G30" s="2" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="31">
       <c r="G31" s="2" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>COMMOWN</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>17.76</v>
+      </c>
     </row>
     <row r="32">
       <c r="G32" s="2" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MR OU MME HOONAKKER PHILIPPE /MOTIF DON DE PAPA MAMAN</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>30000</v>
+      </c>
     </row>
     <row r="33">
       <c r="G33" s="2" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>AUCHAN SUPERMAR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="34">
       <c r="G34" s="2" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>96.48999999999999</v>
+      </c>
     </row>
     <row r="35">
       <c r="G35" s="2" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>18/07/2025</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>MC DONALD S STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="36">
       <c r="G36" s="2" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>17/07/2025</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PAYPAL *900CARE LUXEMBOURG</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>36.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="G37" s="2" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>16/07/2025</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AUCHAN SUPERMAR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="38">
       <c r="G38" s="2" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>VIR SEPA INST RECU /DE MR OU MME HOONAKKER PHILIPPE /REF VIREMENT DE MR OU MME HOONAKKER PHI /MOTIF VIREMENT DE MR OU MME HOONAKKER PHILIPPE</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="39">
       <c r="G39" s="2" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>GOOGLE ONE</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="40">
       <c r="G40" s="2" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="41">
       <c r="G41" s="2" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>OPENAI *CHATGPT</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="G42" s="2" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>23.66</v>
+      </c>
     </row>
     <row r="43">
       <c r="G43" s="2" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>LEROY MERLIN OSTWALD</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>24.9</v>
+      </c>
     </row>
     <row r="44">
       <c r="G44" s="2" t="n"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>60.48</v>
+      </c>
     </row>
     <row r="45">
       <c r="G45" s="2" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>82.89</v>
+      </c>
     </row>
     <row r="46">
       <c r="G46" s="2" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>MC DONALD S STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="47">
       <c r="G47" s="2" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>LOU-ANNE /REFDO INSCRIPTION FAC</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="48">
       <c r="G48" s="2" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT ASSURANCE HABITATION FH</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="49">
       <c r="G49" s="2" t="n"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT EAU FH</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="50">
       <c r="G50" s="2" t="n"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="51">
       <c r="G51" s="2" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2.68</v>
+      </c>
     </row>
     <row r="52">
       <c r="G52" s="2" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>10/07/2025</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>AMZ DIGITAL FRA PAYLI2125856/</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="53">
       <c r="G53" s="2" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>10/07/2025</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>WWW.WANABOAT.FR</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="54">
       <c r="G54" s="2" t="n"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10/07/2025</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS /MOTIF PRIME OBJECTIF /BEN M HOONAKKER FRANK /REFDO /REFBEN</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="55">
       <c r="G55" s="2" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>09/07/2025</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>8.99</v>
+      </c>
     </row>
     <row r="56">
       <c r="G56" s="2" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>09/07/2025</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>43.48</v>
+      </c>
     </row>
     <row r="57">
       <c r="G57" s="2" t="n"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>09/07/2025</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>NOVALIX SAS /MOTIF VIREMENT SAS NOVALIX</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1512.85</v>
+      </c>
     </row>
     <row r="58">
       <c r="G58" s="2" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>08/07/2025</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="59">
       <c r="G59" s="2" t="n"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>08/07/2025</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>SNCF-VOYAGEURS PARIS 10</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>11.5</v>
+      </c>
     </row>
     <row r="60">
       <c r="G60" s="2" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>08/07/2025</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>15.69</v>
+      </c>
     </row>
     <row r="61">
       <c r="G61" s="2" t="n"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>08/07/2025</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT ELECTRICITE FH</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="62">
       <c r="G62" s="2" t="n"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>08/07/2025</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT FREE FH INTRNET ET MOBILE</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="63">
       <c r="G63" s="2" t="n"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>08/07/2025</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE HABITATION FH</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="64">
       <c r="G64" s="2" t="n"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>08/07/2025</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE FONCIERE FH</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="65">
       <c r="G65" s="2" t="n"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>M HOONAKKER FRANK /MOTIF HOT</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="66">
       <c r="G66" s="2" t="n"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>HOTEL KREUZ-PO</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="67">
       <c r="G67" s="2" t="n"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>CULBERSON CHRIST /MOTIF PEA</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="68">
       <c r="G68" s="2" t="n"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>HOTEL KREUZ POS</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>35.8</v>
+      </c>
     </row>
     <row r="69">
       <c r="G69" s="2" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>AMAZON PRIME FR PAYLI2469664/</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>69.90000000000001</v>
+      </c>
     </row>
     <row r="70">
       <c r="G70" s="2" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>92.89</v>
+      </c>
     </row>
     <row r="71">
       <c r="G71" s="2" t="n"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Vt vers : 30004031840003113585558</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="72">
       <c r="G72" s="2" t="n"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>MACIF CENTRE EUROPE PRODUCTION-MACIF</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>117.68</v>
+      </c>
     </row>
     <row r="73">
       <c r="G73" s="2" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>04/07/2025</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ARIANE PIZZA STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="74">
       <c r="G74" s="2" t="n"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>04/07/2025</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>SNCF-VOYAGEURS PARIS 10</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="75">
       <c r="G75" s="2" t="n"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>04/07/2025</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>INTERSPORT STUTZHEIM OFF</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="76">
       <c r="G76" s="2" t="n"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>04/07/2025</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ECHEANCE PRET 03184 60645874 (CAPITAL DU 105,38 EUR)</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>35.88</v>
+      </c>
     </row>
     <row r="77">
       <c r="G77" s="2" t="n"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>04/07/2025</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ECHEANCE PRET 03184 60236534 (CAPITAL DU 502,76 EUR)</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>172.03</v>
+      </c>
     </row>
     <row r="78">
       <c r="G78" s="2" t="n"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>03/07/2025</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>AUCHAN SUPERMAR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>2.19</v>
+      </c>
     </row>
     <row r="79">
       <c r="G79" s="2" t="n"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>03/07/2025</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>5.78</v>
+      </c>
     </row>
     <row r="80">
       <c r="G80" s="2" t="n"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>03/07/2025</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>9.59</v>
+      </c>
     </row>
     <row r="81">
       <c r="G81" s="2" t="n"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="82">
       <c r="G82" s="2" t="n"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>FREE MOBILE</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>5.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="G83" s="2" t="n"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT PRET IMMOBILIER</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>550</v>
+      </c>
     </row>
     <row r="84">
       <c r="G84" s="2" t="n"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>7.79</v>
+      </c>
     </row>
     <row r="85">
       <c r="G85" s="2" t="n"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>MC DONALD S STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="86">
       <c r="G86" s="2" t="n"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT ASSURANCE PRET FH</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="87">
       <c r="G87" s="2" t="n"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT GAZ FH</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="88">
       <c r="G88" s="2" t="n"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT MOIS LA</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>255</v>
+      </c>
     </row>
     <row r="89">
       <c r="G89" s="2" t="n"/>
@@ -20564,12 +21556,61 @@
         <v/>
       </c>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>GOOGLE PLAY APP</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="3">
       <c r="G3" s="2" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MC DONALD S STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="G4" s="2" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CSE NOVALIX /REFDO ANCV 2025 HOONAKKER FRANK</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20598,6 +21639,24 @@
         <v/>
       </c>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>55.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20626,6 +21685,24 @@
         <v/>
       </c>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS /MOTIF EPARGNE /BEN M HOONAKKER FRANK /REFDO /REFBEN</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20654,6 +21731,19 @@
         <v/>
       </c>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOVALIX SAS /MOTIF VIREMENT SAS NOVALIX</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>4116.93</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20682,6 +21772,19 @@
         <v/>
       </c>
       <c r="G8" s="2" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>AMZN MKTP DE*R4</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>110.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20710,6 +21813,19 @@
         <v/>
       </c>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>VIR SEPA INST RECU /DE MME SOPHIE HOONAKKER /REF E861223A16EF4E7EBA894AE2E1FE72EB /MOTIF</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20738,6 +21854,19 @@
         <v/>
       </c>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>EDITIONS DES DERNIERES N /MOTIF VRT EDITIONS DES DERNIERES NOUV NUM 2310060958785</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>5.87</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20766,6 +21895,24 @@
         <v/>
       </c>
       <c r="G11" s="2" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>12.99</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20794,6 +21941,24 @@
         <v/>
       </c>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>6.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20822,6 +21987,24 @@
         <v/>
       </c>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MC DONALD S OBERNAI</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>14.15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20850,6 +22033,24 @@
         <v/>
       </c>
       <c r="G14" s="2" t="n"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>19.35</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20878,6 +22079,24 @@
         <v/>
       </c>
       <c r="G15" s="2" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>21.95</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20906,6 +22125,24 @@
         <v/>
       </c>
       <c r="G16" s="2" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>27.99</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20934,6 +22171,24 @@
         <v/>
       </c>
       <c r="G17" s="2" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>44.99</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20962,6 +22217,19 @@
         <v/>
       </c>
       <c r="G18" s="2" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MOL*ACN TIMING</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20990,6 +22258,19 @@
         <v/>
       </c>
       <c r="G19" s="2" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PARC ALSACE AVE BREITENBACH</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21018,6 +22299,19 @@
         <v/>
       </c>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MOL*PAPILLON BO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>61.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21046,6 +22340,24 @@
         <v/>
       </c>
       <c r="G21" s="2" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>92.89</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -21074,6 +22386,24 @@
         <v/>
       </c>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>4.03</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21102,6 +22432,19 @@
         <v/>
       </c>
       <c r="G23" s="2" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>RETRAIT PEA UFF /MOTIF SDF PEA 51622702001</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>12335.52</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21130,6 +22473,19 @@
         <v/>
       </c>
       <c r="G24" s="2" t="n"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MME CHRISTINE CULBERSON /REFDO RETRAIT UFF</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>6167.76</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21158,195 +22514,1232 @@
         <v/>
       </c>
       <c r="G25" s="2" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS /MOTIF RETRAIT UFF /BEN M HOONAKKER FRANK /REFDO /REFBEN</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>6167.76</v>
+      </c>
     </row>
     <row r="26">
       <c r="G26" s="2" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>COMMOWN</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>17.76</v>
+      </c>
     </row>
     <row r="27">
       <c r="G27" s="2" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LA STUB SCHILTIGHEIM</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="28">
       <c r="G28" s="2" t="n"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>4.47</v>
+      </c>
     </row>
     <row r="29">
       <c r="G29" s="2" t="n"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SNCF-VOYAGEURS PARIS 10</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="30">
       <c r="G30" s="2" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>RESTAURATION LA CELLES SUR PL</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="31">
       <c r="G31" s="2" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MAISON ADAM RAON L ETAPE</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="32">
       <c r="G32" s="2" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>8.9</v>
+      </c>
     </row>
     <row r="33">
       <c r="G33" s="2" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>19.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="G34" s="2" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>35.9</v>
+      </c>
     </row>
     <row r="35">
       <c r="G35" s="2" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>LIDL LINGO 3782 LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>49.26</v>
+      </c>
     </row>
     <row r="36">
       <c r="G36" s="2" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>49.99</v>
+      </c>
     </row>
     <row r="37">
       <c r="G37" s="2" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>58.9</v>
+      </c>
     </row>
     <row r="38">
       <c r="G38" s="2" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>92.89</v>
+      </c>
     </row>
     <row r="39">
       <c r="G39" s="2" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>EPICERIE DES LA CELLES SUR PL</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.55</v>
+      </c>
     </row>
     <row r="40">
       <c r="G40" s="2" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>AMBLUCE LORQUIN</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>3.44</v>
+      </c>
     </row>
     <row r="41">
       <c r="G41" s="2" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>EPICERIE DES LA CELLES SUR PL</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>11.47</v>
+      </c>
     </row>
     <row r="42">
       <c r="G42" s="2" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>HOTEL VELLEDA GRANDFONTAINE</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>12.4</v>
+      </c>
     </row>
     <row r="43">
       <c r="G43" s="2" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>RECEPTION LACS CELLES SUR PL</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>13.91</v>
+      </c>
     </row>
     <row r="44">
       <c r="G44" s="2" t="n"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FOURNIL WINTZ LUTZELBOURG</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>15.06</v>
+      </c>
     </row>
     <row r="45">
       <c r="G45" s="2" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>INTERMARCHE LEMBERG</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>7.51</v>
+      </c>
     </row>
     <row r="46">
       <c r="G46" s="2" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>RADIDALI HENRIDORFF</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="47">
       <c r="G47" s="2" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>MARTIG THIERRY BITCHE</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="48">
       <c r="G48" s="2" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>OPENAI *CHATGPT</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>21.12</v>
+      </c>
     </row>
     <row r="49">
       <c r="G49" s="2" t="n"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>GOOGLE ONE</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="50">
       <c r="G50" s="2" t="n"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>CAMPING HASPELSCHIEDT</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="51">
       <c r="G51" s="2" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>CAMPING HASPELSCHIEDT</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="52">
       <c r="G52" s="2" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>CAMPING DU FLEC LEMBACH</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>9.52</v>
+      </c>
     </row>
     <row r="53">
       <c r="G53" s="2" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>LA BREMENDELL STURZELBRONN</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>18.1</v>
+      </c>
     </row>
     <row r="54">
       <c r="G54" s="2" t="n"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>CAMPING HASPELSCHIEDT</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>18.15</v>
+      </c>
     </row>
     <row r="55">
       <c r="G55" s="2" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AMZ DIGITAL FRA PAYLI2125856/</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="56">
       <c r="G56" s="2" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="57">
       <c r="G57" s="2" t="n"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AREAS STRASBOUR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="58">
       <c r="G58" s="2" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>5.26</v>
+      </c>
     </row>
     <row r="59">
       <c r="G59" s="2" t="n"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>CHEZ MURIEL BOUXWILLER</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>9.15</v>
+      </c>
     </row>
     <row r="60">
       <c r="G60" s="2" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ACCASTILLAGE DI STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="61">
       <c r="G61" s="2" t="n"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SNCF-VOYAGEURS PARIS 10</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>11.5</v>
+      </c>
     </row>
     <row r="62">
       <c r="G62" s="2" t="n"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>22.73</v>
+      </c>
     </row>
     <row r="63">
       <c r="G63" s="2" t="n"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>RESTAURANT WINS WINDSTEIN</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>23.9</v>
+      </c>
     </row>
     <row r="64">
       <c r="G64" s="2" t="n"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>DECATHLON GEISPOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>56.44</v>
+      </c>
     </row>
     <row r="65">
       <c r="G65" s="2" t="n"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>UEP*DAC SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>61.91</v>
+      </c>
     </row>
     <row r="66">
       <c r="G66" s="2" t="n"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>78.89</v>
+      </c>
     </row>
     <row r="67">
       <c r="G67" s="2" t="n"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>DECATHLON GEISPOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>197.98</v>
+      </c>
     </row>
     <row r="68">
       <c r="G68" s="2" t="n"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>M HOONAKKER FRANK /MOTIF TENTE</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="69">
       <c r="G69" s="2" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT ASSURANCE HABITATION FH</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="70">
       <c r="G70" s="2" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT EAU FH</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="71">
       <c r="G71" s="2" t="n"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT ELECTRICITE FH</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="72">
       <c r="G72" s="2" t="n"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT FREE FH INTRNET ET MOBILE</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="73">
       <c r="G73" s="2" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE HABITATION FH</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="74">
       <c r="G74" s="2" t="n"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE FONCIERE FH</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="75">
       <c r="G75" s="2" t="n"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>CULBERSON HOONAK /MOTIF ERREUR VIREMENT VOITURE</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="76">
       <c r="G76" s="2" t="n"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>5.98</v>
+      </c>
     </row>
     <row r="77">
       <c r="G77" s="2" t="n"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>MACIF CENTRE EUROPE PRODUCTION-MACIF</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>117.68</v>
+      </c>
     </row>
     <row r="78">
       <c r="G78" s="2" t="n"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Vt vers : 30004031840003113585558</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="79">
       <c r="G79" s="2" t="n"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="80">
       <c r="G80" s="2" t="n"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>AMZ DIGITAL FRA PAYLI2125856/</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>2.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="G81" s="2" t="n"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>30.64</v>
+      </c>
     </row>
     <row r="82">
       <c r="G82" s="2" t="n"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>ECHEANCE PRET 03184 60645874 (CAPITAL DU 70,47 EUR)</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>35.88</v>
+      </c>
     </row>
     <row r="83">
       <c r="G83" s="2" t="n"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>ECHEANCE PRET 03184 60236534 (CAPITAL DU 335,62 EUR)</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>172.03</v>
+      </c>
     </row>
     <row r="84">
       <c r="G84" s="2" t="n"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>FREE MOBILE</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>5.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="G85" s="2" t="n"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT PRET IMMOBILIER</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>550</v>
+      </c>
     </row>
     <row r="86">
       <c r="G86" s="2" t="n"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT ASSURANCE PRET FH</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="87">
       <c r="G87" s="2" t="n"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT GAZ FH</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="88">
       <c r="G88" s="2" t="n"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT MOIS LA</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>255</v>
+      </c>
     </row>
     <row r="89">
       <c r="G89" s="2" t="n"/>
@@ -21506,12 +23899,61 @@
         <v/>
       </c>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NOVALIX SAS /MOTIF VIREMENT SAS NOVALIX</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>3281.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="G3" s="2" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>21.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="G4" s="2" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>GOOGLE PLAY APP</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21540,6 +23982,24 @@
         <v/>
       </c>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BOULANGERIE KA LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21568,6 +24028,24 @@
         <v/>
       </c>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>11.56</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21596,6 +24074,24 @@
         <v/>
       </c>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21624,6 +24120,24 @@
         <v/>
       </c>
       <c r="G8" s="2" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>LIDL LINGO 3782 LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>22.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21652,6 +24166,24 @@
         <v/>
       </c>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>35.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21680,6 +24212,24 @@
         <v/>
       </c>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>58.13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21708,6 +24258,24 @@
         <v/>
       </c>
       <c r="G11" s="2" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>92.89</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21736,6 +24304,19 @@
         <v/>
       </c>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MME CHRISTINE CULBERSON /MOTIF COURSES</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21764,6 +24345,24 @@
         <v/>
       </c>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MC DONALD S STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21792,6 +24391,19 @@
         <v/>
       </c>
       <c r="G14" s="2" t="n"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PILOTI STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>33.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21820,6 +24432,24 @@
         <v/>
       </c>
       <c r="G15" s="2" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>12.99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21848,6 +24478,19 @@
         <v/>
       </c>
       <c r="G16" s="2" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CARREFOUR ESPLA STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>5.69</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21876,6 +24519,24 @@
         <v/>
       </c>
       <c r="G17" s="2" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>COMMOWN</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>17.76</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21904,6 +24565,24 @@
         <v/>
       </c>
       <c r="G18" s="2" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MHP PRESTATIONS SANTE PLEIADE /MOTIF HOONAKKER FRANK(M252590117B)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>260</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21932,6 +24611,24 @@
         <v/>
       </c>
       <c r="G19" s="2" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>UEP*SUPER U LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>7.02</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21960,6 +24657,24 @@
         <v/>
       </c>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SAS XINGYI STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21988,6 +24703,24 @@
         <v/>
       </c>
       <c r="G21" s="2" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ARIANE PIZZA STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -22016,6 +24749,24 @@
         <v/>
       </c>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>11.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -22044,6 +24795,24 @@
         <v/>
       </c>
       <c r="G23" s="2" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LIDL LINGO 3782 LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>15.15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22072,6 +24841,19 @@
         <v/>
       </c>
       <c r="G24" s="2" t="n"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BILLETTERIE WEB IVRY SUR SEIN</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>39.65</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22100,165 +24882,1077 @@
         <v/>
       </c>
       <c r="G25" s="2" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>92.89</v>
+      </c>
     </row>
     <row r="26">
       <c r="G26" s="2" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>CARREFOUR ESPLA STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>4.38</v>
+      </c>
     </row>
     <row r="27">
       <c r="G27" s="2" t="n"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>28.02</v>
+      </c>
     </row>
     <row r="28">
       <c r="G28" s="2" t="n"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>AUCHAN SUPERMAR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>16.46</v>
+      </c>
     </row>
     <row r="29">
       <c r="G29" s="2" t="n"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SANEF 0909-1509 SENLIS</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>15.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="G30" s="2" t="n"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="G31" s="2" t="n"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SPORTIVISION</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="32">
       <c r="G32" s="2" t="n"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SANEF SENLIS</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="33">
       <c r="G33" s="2" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SANEF SENLIS</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="34">
       <c r="G34" s="2" t="n"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>M HOONAKKER FRANK /MOTIF PHOTOS GRG</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="35">
       <c r="G35" s="2" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>TOTAL KESKATEL</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="36">
       <c r="G36" s="2" t="n"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>BENOIT MICHELS BE BOUILLON</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="37">
       <c r="G37" s="2" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>EG KFC LONGEVIL LONGEV573482/</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>11.9</v>
+      </c>
     </row>
     <row r="38">
       <c r="G38" s="2" t="n"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>MC DONALD S STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="G39" s="2" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>IL PADRINO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>19.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="G40" s="2" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>OPENAI *CHATGPT</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="G41" s="2" t="n"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>BISTRO PAPILLON</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>29.3</v>
+      </c>
     </row>
     <row r="42">
       <c r="G42" s="2" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>58.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="G43" s="2" t="n"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PAYPAL *LANGUAG LUXEMBOURG</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>59.89</v>
+      </c>
     </row>
     <row r="44">
       <c r="G44" s="2" t="n"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>96.48999999999999</v>
+      </c>
     </row>
     <row r="45">
       <c r="G45" s="2" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>GOOGLE ONE</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="46">
       <c r="G46" s="2" t="n"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>THAI SWAN</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>37.7</v>
+      </c>
     </row>
     <row r="47">
       <c r="G47" s="2" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT ASSURANCE HABITATION FH</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="48">
       <c r="G48" s="2" t="n"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>LW*BILLETWEB PARIS 7</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="49">
       <c r="G49" s="2" t="n"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT EAU FH</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="50">
       <c r="G50" s="2" t="n"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>SELECTA SAS</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="51">
       <c r="G51" s="2" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SNCF-VOYAGEURS PARIS 10</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="52">
       <c r="G52" s="2" t="n"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>SNCF-VOYAGEURS PARIS 10</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="53">
       <c r="G53" s="2" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>LIDL LINGO 3782 LINGOLSHEIM</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>72.70999999999999</v>
+      </c>
     </row>
     <row r="54">
       <c r="G54" s="2" t="n"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SELARL DR NINIS STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>265.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="G55" s="2" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AMZ DIGITAL FRA PAYLI2125856/</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="56">
       <c r="G56" s="2" t="n"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>MME CHRISTINE CULBERSON /MOTIF PERCEUSE</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="57">
       <c r="G57" s="2" t="n"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AUCHAN SUPERMAR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>3.79</v>
+      </c>
     </row>
     <row r="58">
       <c r="G58" s="2" t="n"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SPORT TICKETING BIDART</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>74.05</v>
+      </c>
     </row>
     <row r="59">
       <c r="G59" s="2" t="n"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>82.48999999999999</v>
+      </c>
     </row>
     <row r="60">
       <c r="G60" s="2" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT ELECTRICITE FH</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="61">
       <c r="G61" s="2" t="n"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT FREE FH INTRNET ET MOBILE</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="62">
       <c r="G62" s="2" t="n"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE HABITATION FH</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="63">
       <c r="G63" s="2" t="n"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT TAXE FONCIERE FH</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="64">
       <c r="G64" s="2" t="n"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>AUCHAN SUPERMAR STRASBOURG</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>10.61</v>
+      </c>
     </row>
     <row r="65">
       <c r="G65" s="2" t="n"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Vt vers : 30004031840003113585558</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="66">
       <c r="G66" s="2" t="n"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>MACIF CENTRE EUROPE PRODUCTION-MACIF</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>117.68</v>
+      </c>
     </row>
     <row r="67">
       <c r="G67" s="2" t="n"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>23.74</v>
+      </c>
     </row>
     <row r="68">
       <c r="G68" s="2" t="n"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>ECHEANCE PRET 03184 60645874 (CAPITAL DU 35,35 EUR)</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>35.88</v>
+      </c>
     </row>
     <row r="69">
       <c r="G69" s="2" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ECHEANCE PRET 03184 60236534 (CAPITAL DU 168,03 EUR)</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>172.03</v>
+      </c>
     </row>
     <row r="70">
       <c r="G70" s="2" t="n"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>AMAZON PAYMENTS PAYLI2441535/</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>19.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="G71" s="2" t="n"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>FREE MOBILE</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>5.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="G72" s="2" t="n"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PAYPAL EUROPE S.A.R.L. ET CIE S.C.A</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>161.95</v>
+      </c>
     </row>
     <row r="73">
       <c r="G73" s="2" t="n"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT PRET IMMOBILIER</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>550</v>
+      </c>
     </row>
     <row r="74">
       <c r="G74" s="2" t="n"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>QUITOQUE PARIS</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>92.89</v>
+      </c>
     </row>
     <row r="75">
       <c r="G75" s="2" t="n"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL PAYLI2090401/</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>106.25</v>
+      </c>
     </row>
     <row r="76">
       <c r="G76" s="2" t="n"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT ASSURANCE PRET FH</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="77">
       <c r="G77" s="2" t="n"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>VIR CPTE A CPTE EMIS VR.PERMANENT GAZ FH</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="78">
       <c r="G78" s="2" t="n"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>VIREMENT FAVEUR TIERS VR.PERMANENT MOIS LA</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>255</v>
+      </c>
     </row>
     <row r="79">
       <c r="G79" s="2" t="n"/>
